--- a/Assets/Config/Excel/RedDot.xlsx
+++ b/Assets/Config/Excel/RedDot.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -535,13 +535,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>0</v>
       </c>
@@ -552,7 +550,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>main.mail</t>
@@ -573,7 +570,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>main.mail.unread</t>
@@ -594,7 +590,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>main.activity</t>
@@ -615,7 +610,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>main.activity.limited</t>
@@ -636,7 +630,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>main.activity.checkin</t>
@@ -657,7 +650,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>main.friend</t>
@@ -678,7 +670,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>main.friend.request</t>
@@ -699,7 +690,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>main.bag</t>
@@ -716,6 +706,126 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>背包</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>main.collection</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>收藏</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>main.collection.sheep</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>main.collection</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>羊图鉴有新羊</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>main.collection.sheep.1001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>main.collection.sheep</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>羊1001未读</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>main.collection.sheep.1002</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>main.collection.sheep</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>羊1002未读</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>main.collection.sheep.1003</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>main.collection.sheep</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>羊1003未读</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>main.collection.sheep.1004</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>main.collection.sheep</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>羊1004未读</t>
         </is>
       </c>
     </row>

--- a/Assets/Config/Excel/RedDot.xlsx
+++ b/Assets/Config/Excel/RedDot.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -709,126 +709,6 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>main.collection</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>main</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>收藏</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>main.collection.sheep</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>main.collection</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>羊图鉴有新羊</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>main.collection.sheep.1001</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>main.collection.sheep</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>羊1001未读</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>main.collection.sheep.1002</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>main.collection.sheep</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>羊1002未读</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>main.collection.sheep.1003</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>main.collection.sheep</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>羊1003未读</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>main.collection.sheep.1004</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>main.collection.sheep</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>羊1004未读</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Config/Excel/RedDot.xlsx
+++ b/Assets/Config/Excel/RedDot.xlsx
@@ -535,11 +535,13 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>main</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>0</v>
       </c>
@@ -550,6 +552,7 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>main.mail</t>
@@ -570,6 +573,7 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>main.mail.unread</t>
@@ -590,6 +594,7 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>main.activity</t>
@@ -610,6 +615,7 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>main.activity.limited</t>
@@ -630,6 +636,7 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>main.activity.checkin</t>
@@ -650,6 +657,7 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>main.friend</t>
@@ -670,6 +678,7 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>main.friend.request</t>
@@ -690,6 +699,7 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>main.bag</t>
